--- a/public/templates/employee-import-template.xlsx
+++ b/public/templates/employee-import-template.xlsx
@@ -480,13 +480,13 @@
     <t>ET0006-พนักงานรายวัน</t>
   </si>
   <si>
-    <t>ET0007-พนักงานพาร์ตไทม์</t>
-  </si>
-  <si>
-    <t>ET0008-พนักงานพาร์ตไทม์</t>
-  </si>
-  <si>
-    <t>ET0009-พนักงานพาร์ตไทม์</t>
+    <t>ET0007-พนักงานพาร์ททาม</t>
+  </si>
+  <si>
+    <t>ET0008-พนักงานพาร์ททาม</t>
+  </si>
+  <si>
+    <t>ET0009-พนักงานพาร์ททาม</t>
   </si>
   <si>
     <t>ET00010-พนักงานเหมาจ่าย</t>
@@ -5885,7 +5885,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" prompt="B0001" sqref="AO4">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" prompt="KBANK" sqref="AP4">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -5927,7 +5927,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO5">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP5">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -5969,7 +5969,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO6">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP6">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6011,7 +6011,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO7">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP7">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6053,7 +6053,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO8">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP8">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6095,7 +6095,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO9">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP9">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6137,7 +6137,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO10">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP10">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6179,7 +6179,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO11">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP11">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6221,7 +6221,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO12">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP12">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6263,7 +6263,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO13">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP13">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6305,7 +6305,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO14">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP14">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6347,7 +6347,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO15">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP15">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6389,7 +6389,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO16">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP16">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6431,7 +6431,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO17">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP17">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6473,7 +6473,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO18">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP18">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6515,7 +6515,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO19">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP19">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6557,7 +6557,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO20">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP20">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6599,7 +6599,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO21">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP21">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6641,7 +6641,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO22">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP22">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6683,7 +6683,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO23">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP23">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6725,7 +6725,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO24">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP24">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6767,7 +6767,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO25">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP25">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6809,7 +6809,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO26">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP26">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6851,7 +6851,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO27">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP27">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6893,7 +6893,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO28">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP28">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6935,7 +6935,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO29">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP29">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -6977,7 +6977,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO30">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP30">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7019,7 +7019,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO31">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP31">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7061,7 +7061,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO32">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP32">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7103,7 +7103,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO33">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP33">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7145,7 +7145,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO34">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP34">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7187,7 +7187,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO35">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP35">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7229,7 +7229,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO36">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP36">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7271,7 +7271,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO37">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP37">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7313,7 +7313,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO38">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP38">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7355,7 +7355,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO39">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP39">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7397,7 +7397,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO40">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP40">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7439,7 +7439,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO41">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP41">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7481,7 +7481,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO42">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP42">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7523,7 +7523,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO43">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP43">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7565,7 +7565,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO44">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP44">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7607,7 +7607,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO45">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP45">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7649,7 +7649,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO46">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP46">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7691,7 +7691,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO47">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP47">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7733,7 +7733,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO48">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP48">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7775,7 +7775,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO49">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP49">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7817,7 +7817,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO50">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP50">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7859,7 +7859,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO51">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP51">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7901,7 +7901,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO52">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP52">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
@@ -7943,7 +7943,7 @@
       <formula1>"0-เงินสด,1-โอน,2-เช็ค"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AO53">
-      <formula1>""</formula1>
+      <formula1>"B0001"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Input error" error="Value is not in list." promptTitle="กรุณาเลือก" sqref="AP53">
       <formula1>"TTB,BankThai,TISCO,DBS,KKP,KBANK,PromptPay,SMBC,BAY,ISBT,HSBC,MHBK,CIMB,Other,ICBC,BBL,LHBANK,SMEBANK,GHB,KTB,BAAC,GSB,CITI,ACL,MICB,SC,UOB,SCIB,SCB"</formula1>
